--- a/pacjenci/HALINA LEWIŃSKA.xlsx
+++ b/pacjenci/HALINA LEWIŃSKA.xlsx
@@ -485,12 +485,12 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -529,12 +529,12 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -542,17 +542,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>
@@ -573,12 +573,12 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Inne</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Do oceny</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -586,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CR</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
+          <t>4 - utrzymujący się wychwyt patologiczny</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
+          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
         </is>
       </c>
     </row>

--- a/pacjenci/HALINA LEWIŃSKA.xlsx
+++ b/pacjenci/HALINA LEWIŃSKA.xlsx
@@ -413,191 +413,143 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>08.02.2022</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy. Ocena stopnia zaawansowania.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 79mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne szyjne: - po stronie lewej grup 2, 3, 4, 5 średnicy wg PET do 22mm, SUV max do 8,0, - po stronie prawej grup 2, 3, 4, 5 łączące się z przytchawiczymi najwyższymi po stronie lewej wielkości wg PET do 43x63x99mm, SUV max do 8,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne: - w śródpiersiu przednim i przymostkowe obustronnie średnicy wg PET do 12mm, SUV max do 6,0 - położone przy łuku aorty po stronie lewej  średnicy wg PET do 18mm, SUV max do 5,5, - przytchawicze po stronie prawej  średnicy wg PET do 26mm, SUV max do 6,9, - okna aortalno-płucnego średnicy wg PET do 31mm, SUV max do 7,0, - przyosierdziu po stronie prawej  średnicy wg PET do 9mm, SUV max do 5,4, - wnęki płuca lewego średnicy wg PET 16mm, SUV  max 5,3, - wnęki płuca prawego średnicy wg PET 33mm, SUV max 6,5,  - podostrogowe wielkości wg PET do 49x26mm, SUV max do 8,7, - pomiędzy żyłą płucną lewą a aortą średnicy wg PET do 15mm, SUV max do 8,8,  - w zachyłkach przeponowo-sercowych przednich obustronnie średnicy wg PET do 12mm, SUV max do 5,0, - pachowe po stronie lewej wielkości wg PET do 39x68mm, SUV max do 10,5, - pachowe po stronie prawej  średnicy wg PET do 52x39mm, SUV max do 10,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Grzbietowo w płatach dolnych zmiany bliznowato-włókniste, poza tym obustronnie zmiany rozedmowe i zaburzenia perfuzji  w miąższu obu płuc - do oceny klinicznej.  Brzuch i miednica: Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne: - w okolicy krzywizny mniejszej żołądka wielkości wg PET do 52x76mm, SUV max do 9,6, - przyaortalne po stronie lewej wielkości wg PET do 46x74x198mm, SUV max do 11,7, - przyaortalne po stronie prawej wielkości wg PET do 30x70x215mm, SUV max do 9,1,   - krezkowe i położone do przodu od talerzy biodrowych średnicy wg PET do 26mm, SUV max 7,3, - biodrowe wspólne, wewnętrzne, zewnętrze, pachwinowe i udowe lewe wielkości wg PET 77x51mm, SUV max do 12,9, - biodrowe wspólne, wewnętrzne, zewnętrze, pachwinowe i udowe prawe wielkości wg PET 49x54mm, SUV max do 10,8, - w okolicy przedkrzyżowe średnicy wg PET do 21mm, SUV max do 8,0, - do tyłu od trzonu kości biodrowej lewej średnicy wg PET 13mm, SUV max 6,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy ze złogami wielkości do 17 mm. Zastój w UKM nerki prawej. Zwapnienia w trzonie macicy.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym (zwłaszcza w odcinku lędźwiowym kregosłupa i kościach miednicy) - do oceny z obrazem klinicznym i wynikiem trepanobiopsji.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, dyskopatia L4/5 i L5/S1.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax Prawy płat wątroby SUVmax do 1,9.</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony.  Niejednorodny metabolizm FDG w układzie kostnym (zwłaszcza w odcinku lędźwiowym kregosłupa i kościach miednicy) - do oceny z obrazem klinicznym i wynikiem trepanobiopsji.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>12.9</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>16.08.2022</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy st zaawansowania wg Lugano III/IV. Ocena odpowiedzi po 4 cyklach Obinutuzumab+ CVP.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 120 mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hyperostosis frontalis. Hypoplazja zatok czołowych. Komory boczne mózgu poszerzone - wyraźny zanik podkorowy mózgu. Wydatne zgrubienia błony śluzowej w sitowiu po stronie lewej oraz niewielkie po stronie prawej. Niewielkie prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę prawą. Spakietowane węzły chłonne szyjne po stronie lewej: grupy 4 z węzłami chłonnymi przytchawiczymi lewymi, wielkości do 29x30x37 mm. Węzły chłonne szyjne grupy 5 po stronie prawej wielkości do 14x17 mm oraz do 17x15mm po stronie lewej. Ok. 6mm zwapnienie w prawym płacie tarczycy.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze i spakietowane węzły chłonne: - w śródpiersiu przednim  średnicy do 9 mm; - lewostronnie od łuku aorty wielkości do 8x17 mm; - przytchawicze po stronie prawej  średnicy do 11 mm; - okna aortalno-płucnego do 16 mm; - przy osierdziu po stronie prawej  średnicy do 6 mm; - podostrogowe wielkości do 17x13x22 mm; - w zachyłkach przeponowo-sercowych przednich do 9 mm;  - pachowe po stronie lewej wielkości do 30x18 mm; - pachowe po stronie prawej wielkości do 30x16 mm (SUV max do 1,6).  Niewielkie zmiany włókniste w szczytach obu płuc. Ok. 17mm pęcherz rozedmowy u podstawy płata górnego płuca lewego. Niewielkie zmiany rozedmowo-włókniste w segmentach grzbietowych płatów dolnych obu płuc.  Brzuch i miednica: Ogniskowo wzmożony metabolizm FDG w odbytnicy SUV max do 7,0- do kontroli w badaniu endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masy miękkotkankowe (dokładna ocena wielkości mas resztkowych możliwa jest w badaniu TK z kontrastem dożylnym): - okołoaortalnie, obustronnie od poziomu odejścia tętnicy krezkowej górnej do rozwidlenia, wielkości do ok. 84x34x96mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych, wielkości do ok. 45x36mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych, wielkości do ok. 36x32mm.  Pojedyncze i spakietowane węzły chłonne: - w okolicy krzywizny mniejszej żołądka wielkości do 16 mm; - pachwinowe lewe [więcej i większe], wielkości do 22x34 mm; - pachwinowe prawe wielkości do 16x14mm. Pęcherzyk żółciowy o znacznie pogrubiałej ścianie w przeglądowym badaniu TK, z częściowo uwapnionymi konkrementami, wielkości do 17 mm - calculus cholecystitis?. Nefrostomia po stronie prawej. Liczne zwapnienia w trzonie macicy - macica mięśniakowata.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wrodzony blok kostny na poziomie C3-C4, ze śladową, szczątkową tarczą międzykręgową  Dyskopatie na poziomach: L4/L5 [z nierównym obrysem blaszek granicznych trzonów kręgowych i objawem próżni krążka międzykręgowego] i L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach krzyżowo-biodrowych. Os sacrum arcuatum. Ok. 5mm ognisko sklerotyczne w głowie lewej kości ramiennej. Obwodowy obszar osteolityczny w głowie prawej kości ramiennej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 2,4.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej - dobra odpowiedź metaboliczna choroby na stosowane leczenie, z częściową regresją radiologiczną zmian. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>7</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>29.11.2022</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak grudkowy st zaawansowania wg Lugano III/IV. Ocena remisji choroby.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62min od podania 18F-FDG. Glikemia: 149mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hyperostosis frontalis. Hypoplazja zatok czołowych. Komory boczne mózgu poszerzone - wyraźny zanik podkorowy mózgu. Wydatne zgrubienia błony śluzowej w sitowiu po stronie lewej oraz niewielkie po stronie prawej. Niewielkie prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę prawą. Drobne zgrubienia błony śluzowej w obu zatokach szczękowych. Ok. 6mm zwapnienie w prawym płacie tarczycy.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe wielkości do 20mm.  Pojedyncze węzły chłonne w środpiersiu wielkości do 10mm. Niewielkie zmiany włókniste w szczytach obu płuc. Ok. 17mm pęcherz rozedmowy u podstawy płata górnego płuca lewego. Niewielkie zmiany rozedmowo-włókniste w segmentach grzbietowych płatów dolnych obu płuc. Liczne zwapnienia w obu piersiach.  Brzuch i miednica: Ogniskowo wzmożony metabolizm FDG w odbytnicy SUV max do 7,0- do kontroli w badaniu endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masy miękkotkankowe (dokładna ocena wielkości mas resztkowych możliwa jest w badaniu TK z kontrastem dożylnym): - okołoaortalnie, obustronnie od poziomu odejścia tętnicy krezkowej górnej do rozwidlenia, wielkości do ok. 81x31x73mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych, wielkości do ok. 31x37mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych, wielkości do ok. 28x32mm.  Węzły chłonne pachwinowe wielkości do 17mm.  Pęcherzyk żółciowy o znacznie pogrubiałej ścianie w przeglądowym badaniu TK, z częściowo uwapnionymi konkrementami, wielkości do 17 mm - calculus cholecystitis?. Liczne zwapnienia w trzonie macicy - macica mięśniakowata.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wrodzony blok kostny na poziomie C3-C4, ze śladową, szczątkową tarczą międzykręgową  Dyskopatie na poziomach: L4/L5 [z nierównym obrysem blaszek granicznych trzonów kręgowych i objawem próżni krążka międzykręgowego] i L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach krzyżowo-biodrowych. Os sacrum arcuatum. Ok. 5mm ognisko sklerotyczne w głowie lewej kości ramiennej. Obwodowy obszar osteolityczny w głowie prawej kości ramiennej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 2,9.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>7</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/pacjenci/HALINA LEWIŃSKA.xlsx
+++ b/pacjenci/HALINA LEWIŃSKA.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Nr badania</t>
+          <t>Nr PET</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -439,17 +439,42 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Opis badania</t>
+          <t>Glikemia</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Czas po FDG</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Głowa i szyja</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Klatka piersiowa</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Brzuch i miednica</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Układ kostny</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Wnioski</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SUVmax</t>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>SUVmax_global</t>
         </is>
       </c>
     </row>
@@ -469,20 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58min od podania 18F-FDG. Glikemia: 79mg%</t>
+          <t>od szczytu głowy do 1/3 ud</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>: Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne szyjne: - po stronie lewej grup 2, 3, 4, 5 średnicy wg PET do 22mm, SUV max do 8,0, - po stronie prawej grup 2, 3, 4, 5 łączące się z przytchawiczymi najwyższymi po stronie lewej wielkości wg PET do 43x63x99mm, SUV max do 8,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.  Klatka piersiowa i śródpiersie: Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne: - w śródpiersiu przednim i przymostkowe obustronnie średnicy wg PET do 12mm, SUV max do 6,0 - położone przy łuku aorty po stronie lewej  średnicy wg PET do 18mm, SUV max do 5,5, - przytchawicze po stronie prawej  średnicy wg PET do 26mm, SUV max do 6,9, - okna aortalno-płucnego średnicy wg PET do 31mm, SUV max do 7,0, - przyosierdziu po stronie prawej  średnicy wg PET do 9mm, SUV max do 5,4, - wnęki płuca lewego średnicy wg PET 16mm, SUV  max 5,3, - wnęki płuca prawego średnicy wg PET 33mm, SUV max 6,5,  - podostrogowe wielkości wg PET do 49x26mm, SUV max do 8,7, - pomiędzy żyłą płucną lewą a aortą średnicy wg PET do 15mm, SUV max do 8,8,  - w zachyłkach przeponowo-sercowych przednich obustronnie średnicy wg PET do 12mm, SUV max do 5,0, - pachowe po stronie lewej wielkości wg PET do 39x68mm, SUV max do 10,5, - pachowe po stronie prawej  średnicy wg PET do 52x39mm, SUV max do 10,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Grzbietowo w płatach dolnych zmiany bliznowato-włókniste, poza tym obustronnie zmiany rozedmowe i zaburzenia perfuzji  w miąższu obu płuc - do oceny klinicznej.  Brzuch i miednica: Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne: - w okolicy krzywizny mniejszej żołądka wielkości wg PET do 52x76mm, SUV max do 9,6, - przyaortalne po stronie lewej wielkości wg PET do 46x74x198mm, SUV max do 11,7, - przyaortalne po stronie prawej wielkości wg PET do 30x70x215mm, SUV max do 9,1,   - krezkowe i położone do przodu od talerzy biodrowych średnicy wg PET do 26mm, SUV max 7,3, - biodrowe wspólne, wewnętrzne, zewnętrze, pachwinowe i udowe lewe wielkości wg PET 77x51mm, SUV max do 12,9, - biodrowe wspólne, wewnętrzne, zewnętrze, pachwinowe i udowe prawe wielkości wg PET 49x54mm, SUV max do 10,8, - w okolicy przedkrzyżowe średnicy wg PET do 21mm, SUV max do 8,0, - do tyłu od trzonu kości biodrowej lewej średnicy wg PET 13mm, SUV max 6,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy ze złogami wielkości do 17 mm. Zastój w UKM nerki prawej. Zwapnienia w trzonie macicy.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym (zwłaszcza w odcinku lędźwiowym kregosłupa i kościach miednicy) - do oceny z obrazem klinicznym i wynikiem trepanobiopsji.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, dyskopatia L4/5 i L5/S1.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax Prawy płat wątroby SUVmax do 1,9.</t>
+          <t>79</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne szyjne: - po stronie lewej grup 2, 3, 4, 5 średnicy wg PET do 22mm, SUV max do 8,0, - po stronie prawej grup 2, 3, 4, 5 łączące się z przytchawiczymi najwyższymi po stronie lewej wielkości wg PET do 43x63x99mm, SUV max do 8,0. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne: - w śródpiersiu przednim i przymostkowe obustronnie średnicy wg PET do 12mm, SUV max do 6,0 - położone przy łuku aorty po stronie lewej  średnicy wg PET do 18mm, SUV max do 5,5, - przytchawicze po stronie prawej  średnicy wg PET do 26mm, SUV max do 6,9, - okna aortalno-płucnego średnicy wg PET do 31mm, SUV max do 7,0, - przyosierdziu po stronie prawej  średnicy wg PET do 9mm, SUV max do 5,4, - wnęki płuca lewego średnicy wg PET 16mm, SUV  max 5,3, - wnęki płuca prawego średnicy wg PET 33mm, SUV max 6,5,  - podostrogowe wielkości wg PET do 49x26mm, SUV max do 8,7, - pomiędzy żyłą płucną lewą a aortą średnicy wg PET do 15mm, SUV max do 8,8,  - w zachyłkach przeponowo-sercowych przednich obustronnie średnicy wg PET do 12mm, SUV max do 5,0, - pachowe po stronie lewej wielkości wg PET do 39x68mm, SUV max do 10,5, - pachowe po stronie prawej  średnicy wg PET do 52x39mm, SUV max do 10,2. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Grzbietowo w płatach dolnych zmiany bliznowato-włókniste, poza tym obustronnie zmiany rozedmowe i zaburzenia perfuzji  w miąższu obu płuc - do oceny klinicznej.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Spakietowane i pojedyncze aktywne metaboliczne węzły chłonne: - w okolicy krzywizny mniejszej żołądka wielkości wg PET do 52x76mm, SUV max do 9,6, - przyaortalne po stronie lewej wielkości wg PET do 46x74x198mm, SUV max do 11,7, - przyaortalne po stronie prawej wielkości wg PET do 30x70x215mm, SUV max do 9,1,   - krezkowe i położone do przodu od talerzy biodrowych średnicy wg PET do 26mm, SUV max 7,3, - biodrowe wspólne, wewnętrzne, zewnętrze, pachwinowe i udowe lewe wielkości wg PET 77x51mm, SUV max do 12,9, - biodrowe wspólne, wewnętrzne, zewnętrze, pachwinowe i udowe prawe wielkości wg PET 49x54mm, SUV max do 10,8, - w okolicy przedkrzyżowe średnicy wg PET do 21mm, SUV max do 8,0, - do tyłu od trzonu kości biodrowej lewej średnicy wg PET 13mm, SUV max 6,9. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Pęcherzyk żółciowy ze złogami wielkości do 17 mm. Zastój w UKM nerki prawej. Zwapnienia w trzonie macicy.</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Niejednorodny metabolizm FDG w układzie kostnym (zwłaszcza w odcinku lędźwiowym kregosłupa i kościach miednicy) - do oceny z obrazem klinicznym i wynikiem trepanobiopsji.  Poza tym fizjologiczny metabolizm FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa, dyskopatia L4/5 i L5/S1.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony.  Niejednorodny metabolizm FDG w układzie kostnym (zwłaszcza w odcinku lędźwiowym kregosłupa i kościach miednicy) - do oceny z obrazem klinicznym i wynikiem trepanobiopsji.</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="L2" t="n">
         <v>12.9</v>
       </c>
     </row>
@@ -502,20 +552,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59 min od podania 18F-FDG. Glikemia: 120 mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hyperostosis frontalis. Hypoplazja zatok czołowych. Komory boczne mózgu poszerzone - wyraźny zanik podkorowy mózgu. Wydatne zgrubienia błony śluzowej w sitowiu po stronie lewej oraz niewielkie po stronie prawej. Niewielkie prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę prawą. Spakietowane węzły chłonne szyjne po stronie lewej: grupy 4 z węzłami chłonnymi przytchawiczymi lewymi, wielkości do 29x30x37 mm. Węzły chłonne szyjne grupy 5 po stronie prawej wielkości do 14x17 mm oraz do 17x15mm po stronie lewej. Ok. 6mm zwapnienie w prawym płacie tarczycy.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze i spakietowane węzły chłonne: - w śródpiersiu przednim  średnicy do 9 mm; - lewostronnie od łuku aorty wielkości do 8x17 mm; - przytchawicze po stronie prawej  średnicy do 11 mm; - okna aortalno-płucnego do 16 mm; - przy osierdziu po stronie prawej  średnicy do 6 mm; - podostrogowe wielkości do 17x13x22 mm; - w zachyłkach przeponowo-sercowych przednich do 9 mm;  - pachowe po stronie lewej wielkości do 30x18 mm; - pachowe po stronie prawej wielkości do 30x16 mm (SUV max do 1,6).  Niewielkie zmiany włókniste w szczytach obu płuc. Ok. 17mm pęcherz rozedmowy u podstawy płata górnego płuca lewego. Niewielkie zmiany rozedmowo-włókniste w segmentach grzbietowych płatów dolnych obu płuc.  Brzuch i miednica: Ogniskowo wzmożony metabolizm FDG w odbytnicy SUV max do 7,0- do kontroli w badaniu endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masy miękkotkankowe (dokładna ocena wielkości mas resztkowych możliwa jest w badaniu TK z kontrastem dożylnym): - okołoaortalnie, obustronnie od poziomu odejścia tętnicy krezkowej górnej do rozwidlenia, wielkości do ok. 84x34x96mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych, wielkości do ok. 45x36mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych, wielkości do ok. 36x32mm.  Pojedyncze i spakietowane węzły chłonne: - w okolicy krzywizny mniejszej żołądka wielkości do 16 mm; - pachwinowe lewe [więcej i większe], wielkości do 22x34 mm; - pachwinowe prawe wielkości do 16x14mm. Pęcherzyk żółciowy o znacznie pogrubiałej ścianie w przeglądowym badaniu TK, z częściowo uwapnionymi konkrementami, wielkości do 17 mm - calculus cholecystitis?. Nefrostomia po stronie prawej. Liczne zwapnienia w trzonie macicy - macica mięśniakowata.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wrodzony blok kostny na poziomie C3-C4, ze śladową, szczątkową tarczą międzykręgową  Dyskopatie na poziomach: L4/L5 [z nierównym obrysem blaszek granicznych trzonów kręgowych i objawem próżni krążka międzykręgowego] i L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach krzyżowo-biodrowych. Os sacrum arcuatum. Ok. 5mm ognisko sklerotyczne w głowie lewej kości ramiennej. Obwodowy obszar osteolityczny w głowie prawej kości ramiennej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,6; Prawy płat wątroby SUVmax do 2,4.</t>
+          <t>120</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hyperostosis frontalis. Hypoplazja zatok czołowych. Komory boczne mózgu poszerzone - wyraźny zanik podkorowy mózgu. Wydatne zgrubienia błony śluzowej w sitowiu po stronie lewej oraz niewielkie po stronie prawej. Niewielkie prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę prawą. Spakietowane węzły chłonne szyjne po stronie lewej: grupy 4 z węzłami chłonnymi przytchawiczymi lewymi, wielkości do 29x30x37 mm. Węzły chłonne szyjne grupy 5 po stronie prawej wielkości do 14x17 mm oraz do 17x15mm po stronie lewej. Ok. 6mm zwapnienie w prawym płacie tarczycy.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Pojedyncze i spakietowane węzły chłonne: - w śródpiersiu przednim  średnicy do 9 mm; - lewostronnie od łuku aorty wielkości do 8x17 mm; - przytchawicze po stronie prawej  średnicy do 11 mm; - okna aortalno-płucnego do 16 mm; - przy osierdziu po stronie prawej  średnicy do 6 mm; - podostrogowe wielkości do 17x13x22 mm; - w zachyłkach przeponowo-sercowych przednich do 9 mm;  - pachowe po stronie lewej wielkości do 30x18 mm; - pachowe po stronie prawej wielkości do 30x16 mm (SUV max do 1,6).  Niewielkie zmiany włókniste w szczytach obu płuc. Ok. 17mm pęcherz rozedmowy u podstawy płata górnego płuca lewego. Niewielkie zmiany rozedmowo-włókniste w segmentach grzbietowych płatów dolnych obu płuc.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ogniskowo wzmożony metabolizm FDG w odbytnicy SUV max do 7,0- do kontroli w badaniu endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masy miękkotkankowe (dokładna ocena wielkości mas resztkowych możliwa jest w badaniu TK z kontrastem dożylnym): - okołoaortalnie, obustronnie od poziomu odejścia tętnicy krezkowej górnej do rozwidlenia, wielkości do ok. 84x34x96mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych, wielkości do ok. 45x36mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych, wielkości do ok. 36x32mm.  Pojedyncze i spakietowane węzły chłonne: - w okolicy krzywizny mniejszej żołądka wielkości do 16 mm; - pachwinowe lewe [więcej i większe], wielkości do 22x34 mm; - pachwinowe prawe wielkości do 16x14mm. Pęcherzyk żółciowy o znacznie pogrubiałej ścianie w przeglądowym badaniu TK, z częściowo uwapnionymi konkrementami, wielkości do 17 mm - calculus cholecystitis?. Nefrostomia po stronie prawej. Liczne zwapnienia w trzonie macicy - macica mięśniakowata.</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wrodzony blok kostny na poziomie C3-C4, ze śladową, szczątkową tarczą międzykręgową  Dyskopatie na poziomach: L4/L5 [z nierównym obrysem blaszek granicznych trzonów kręgowych i objawem próżni krążka międzykręgowego] i L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach krzyżowo-biodrowych. Os sacrum arcuatum. Ok. 5mm ognisko sklerotyczne w głowie lewej kości ramiennej. Obwodowy obszar osteolityczny w głowie prawej kości ramiennej.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej - dobra odpowiedź metaboliczna choroby na stosowane leczenie, z częściową regresją radiologiczną zmian. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="L3" t="n">
         <v>7</v>
       </c>
     </row>
@@ -535,20 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 62min od podania 18F-FDG. Glikemia: 149mg%.</t>
+          <t>od szczytu głowy do 1/3 ud.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hyperostosis frontalis. Hypoplazja zatok czołowych. Komory boczne mózgu poszerzone - wyraźny zanik podkorowy mózgu. Wydatne zgrubienia błony śluzowej w sitowiu po stronie lewej oraz niewielkie po stronie prawej. Niewielkie prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę prawą. Drobne zgrubienia błony śluzowej w obu zatokach szczękowych. Ok. 6mm zwapnienie w prawym płacie tarczycy.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe wielkości do 20mm.  Pojedyncze węzły chłonne w środpiersiu wielkości do 10mm. Niewielkie zmiany włókniste w szczytach obu płuc. Ok. 17mm pęcherz rozedmowy u podstawy płata górnego płuca lewego. Niewielkie zmiany rozedmowo-włókniste w segmentach grzbietowych płatów dolnych obu płuc. Liczne zwapnienia w obu piersiach.  Brzuch i miednica: Ogniskowo wzmożony metabolizm FDG w odbytnicy SUV max do 7,0- do kontroli w badaniu endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masy miękkotkankowe (dokładna ocena wielkości mas resztkowych możliwa jest w badaniu TK z kontrastem dożylnym): - okołoaortalnie, obustronnie od poziomu odejścia tętnicy krezkowej górnej do rozwidlenia, wielkości do ok. 81x31x73mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych, wielkości do ok. 31x37mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych, wielkości do ok. 28x32mm.  Węzły chłonne pachwinowe wielkości do 17mm.  Pęcherzyk żółciowy o znacznie pogrubiałej ścianie w przeglądowym badaniu TK, z częściowo uwapnionymi konkrementami, wielkości do 17 mm - calculus cholecystitis?. Liczne zwapnienia w trzonie macicy - macica mięśniakowata.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wrodzony blok kostny na poziomie C3-C4, ze śladową, szczątkową tarczą międzykręgową  Dyskopatie na poziomach: L4/L5 [z nierównym obrysem blaszek granicznych trzonów kręgowych i objawem próżni krążka międzykręgowego] i L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach krzyżowo-biodrowych. Os sacrum arcuatum. Ok. 5mm ognisko sklerotyczne w głowie lewej kości ramiennej. Obwodowy obszar osteolityczny w głowie prawej kości ramiennej.  Inne: Miażdżyca aorty i tętnic potomnych.  Wartości referencyjne: MBPS SUVmax 1,9; Prawy płat wątroby SUVmax do 2,9.</t>
+          <t>149</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Hyperostosis frontalis. Hypoplazja zatok czołowych. Komory boczne mózgu poszerzone - wyraźny zanik podkorowy mózgu. Wydatne zgrubienia błony śluzowej w sitowiu po stronie lewej oraz niewielkie po stronie prawej. Niewielkie prawowypukłe skrzywienie przegrody nosowej, z ostrogą kostną skierowana na stronę prawą. Drobne zgrubienia błony śluzowej w obu zatokach szczękowych. Ok. 6mm zwapnienie w prawym płacie tarczycy.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Węzły chłonne pachowe wielkości do 20mm.  Pojedyncze węzły chłonne w środpiersiu wielkości do 10mm. Niewielkie zmiany włókniste w szczytach obu płuc. Ok. 17mm pęcherz rozedmowy u podstawy płata górnego płuca lewego. Niewielkie zmiany rozedmowo-włókniste w segmentach grzbietowych płatów dolnych obu płuc. Liczne zwapnienia w obu piersiach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Ogniskowo wzmożony metabolizm FDG w odbytnicy SUV max do 7,0- do kontroli w badaniu endoskopowej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Masy miękkotkankowe (dokładna ocena wielkości mas resztkowych możliwa jest w badaniu TK z kontrastem dożylnym): - okołoaortalnie, obustronnie od poziomu odejścia tętnicy krezkowej górnej do rozwidlenia, wielkości do ok. 81x31x73mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych prawych, wielkości do ok. 31x37mm; - przy naczyniach biodrowych wspólnych, wewnętrznych i zewnętrznych lewych, wielkości do ok. 28x32mm.  Węzły chłonne pachwinowe wielkości do 17mm.  Pęcherzyk żółciowy o znacznie pogrubiałej ścianie w przeglądowym badaniu TK, z częściowo uwapnionymi konkrementami, wielkości do 17 mm - calculus cholecystitis?. Liczne zwapnienia w trzonie macicy - macica mięśniakowata.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Niewielka esowata skolioza kręgosłupa, z rotacją kręgów. Wrodzony blok kostny na poziomie C3-C4, ze śladową, szczątkową tarczą międzykręgową  Dyskopatie na poziomach: L4/L5 [z nierównym obrysem blaszek granicznych trzonów kręgowych i objawem próżni krążka międzykręgowego] i L5/S1. Zmiany zwyrodnieniowo-wytwórcze w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Zmiany zwyrodnieniowe w stawach krzyżowo-biodrowych. Os sacrum arcuatum. Ok. 5mm ognisko sklerotyczne w głowie lewej kości ramiennej. Obwodowy obszar osteolityczny w głowie prawej kości ramiennej.  Inne: Miażdżyca aorty i tętnic potomnych.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>Aktualnie badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnej metabolicznie choroby chłoniakowej. Poza tym, jak w opisie powyżej.</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="L4" t="n">
         <v>7</v>
       </c>
     </row>
